--- a/data/xlsx/sbce_config_kvm_ems_sbce1_sbce2_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems_sbce1_sbce2_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="EMS" sheetId="1" state="visible" r:id="rId3"/>
@@ -1526,23 +1526,23 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>#REF!="ESXI"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B31:B32" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>#REF!&lt;&gt;"SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B39:B42 B46:B47" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43:B44" type="custom">
-      <formula1>#REF!="SBCE"</formula1>
+      <formula1>#ref!="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2220,19 +2220,15 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>#REF!="ESXI"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B32" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>#REF!&lt;&gt;"SBCE"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43" type="custom">
-      <formula1>#REF!="SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2248,7 +2244,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31" type="none">
@@ -2256,6 +2252,10 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B44" type="none">
+      <formula1>$B$10="SBCE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B43" type="none">
       <formula1>$B$10="SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2922,15 +2922,15 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B5" type="custom">
-      <formula1>#REF!="ESXI"</formula1>
+      <formula1>#ref!="ESXI"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B12 B32" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS+SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS+SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B21:B26" type="custom">
-      <formula1>#REF!&lt;&gt;"SBCE"</formula1>
+      <formula1>#ref!&lt;&gt;"SBCE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B2 B14 B48:B49" type="none">
@@ -2946,7 +2946,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B46:B47" type="custom">
-      <formula1>#REF!&lt;&gt;"EMS"</formula1>
+      <formula1>#ref!&lt;&gt;"EMS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="B31" type="none">

--- a/data/xlsx/sbce_config_kvm_ems_sbce1_sbce2_template.xlsx
+++ b/data/xlsx/sbce_config_kvm_ems_sbce1_sbce2_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="EMS" sheetId="1" state="visible" r:id="rId3"/>
@@ -246,7 +246,7 @@
     <t xml:space="preserve">Time Zone - Time Zone in which device is located  (for example America/Edmonton)</t>
   </si>
   <si>
-    <t xml:space="preserve">ntpservers</t>
+    <t xml:space="preserve">ntpserver</t>
   </si>
   <si>
     <t xml:space="preserve">NTP Server Address: - The IPv4 address for NTP servers.</t>
